--- a/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3DF3474-2718-4CF5-8A81-8A976D7EF4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92A78C63-B196-40CF-A755-100788F9F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="1138">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -106,12 +106,6 @@
     <t>Supercritical Coal</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion*,ep_oil_internal_combustion*</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine*,ep_oil_steam_turbine*</t>
-  </si>
-  <si>
     <t>STG</t>
   </si>
   <si>
@@ -124,24 +118,9 @@
     <t>IGCC</t>
   </si>
   <si>
-    <t>ep_bioenergy*,bioen*</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle*,ep_oil_combined_cycle*,CCGT*,*GasCC*</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine*,ep_oil_gas_turbine*,gas turbine*,EN*CT*</t>
-  </si>
-  <si>
-    <t>ep_coal_CFB*,ep_coal_subcritical*,*subcritical*</t>
-  </si>
-  <si>
     <t>*IGCC*</t>
   </si>
   <si>
-    <t>ep_coal_supercritical*,ep_coal_supercritical_CCS*,ep_coal_ultra-supercritical*,ep_coal_ultra-supercritical_CCS*,*supercritical*</t>
-  </si>
-  <si>
     <t>Gas_Oil Steam</t>
   </si>
   <si>
@@ -334,6 +313,27 @@
     <t>distr*</t>
   </si>
   <si>
+    <t>e*[_]gas_combined_cycle*,e*[_]oil_combined_cycle*,CCGT*,*GasCC*</t>
+  </si>
+  <si>
+    <t>e*[_]gas_internal_combustion*,e*[_]oil_internal_combustion*</t>
+  </si>
+  <si>
+    <t>e*[_]gas_steam_turbine*,e*[_]oil_steam_turbine*</t>
+  </si>
+  <si>
+    <t>e*[_]gas_gas_turbine*,e*[_]oil_gas_turbine*,gas turbine*,EN*CT*</t>
+  </si>
+  <si>
+    <t>e*[_]coal_CFB*,e*[_]coal_subcritical*,*subcritical*</t>
+  </si>
+  <si>
+    <t>e*[_]coal_supercritical*,e*[_]coal_supercritical_CCS*,e*[_]coal_ultra-supercritical*,e*[_]coal_ultra-supercritical_CCS*,*supercritical*</t>
+  </si>
+  <si>
+    <t>e*[_]bioenergy*,bioen*</t>
+  </si>
+  <si>
     <t>~tfm_psets</t>
   </si>
   <si>
@@ -349,3085 +349,3109 @@
     <t>t_pos_andor</t>
   </si>
   <si>
-    <t>p_w50885643</t>
-  </si>
-  <si>
-    <t>e_w50885643*</t>
+    <t>p_w50885643-765_IND</t>
+  </si>
+  <si>
+    <t>e_w50885643-765_IND*</t>
   </si>
   <si>
     <t>OR</t>
   </si>
   <si>
-    <t>p_w97392607</t>
-  </si>
-  <si>
-    <t>e_w97392607*</t>
-  </si>
-  <si>
-    <t>p_w100470285</t>
-  </si>
-  <si>
-    <t>e_w100470285*</t>
-  </si>
-  <si>
-    <t>p_w105373531</t>
-  </si>
-  <si>
-    <t>e_w105373531*</t>
-  </si>
-  <si>
-    <t>p_w131484738</t>
-  </si>
-  <si>
-    <t>e_w131484738*</t>
-  </si>
-  <si>
-    <t>p_w192782338</t>
-  </si>
-  <si>
-    <t>e_w192782338*</t>
-  </si>
-  <si>
-    <t>p_w193216698</t>
-  </si>
-  <si>
-    <t>e_w193216698*</t>
-  </si>
-  <si>
-    <t>p_w195459361</t>
-  </si>
-  <si>
-    <t>e_w195459361*</t>
-  </si>
-  <si>
-    <t>p_w196933682</t>
-  </si>
-  <si>
-    <t>e_w196933682*</t>
-  </si>
-  <si>
-    <t>p_w201845280</t>
-  </si>
-  <si>
-    <t>e_w201845280*</t>
-  </si>
-  <si>
-    <t>p_w202980838</t>
-  </si>
-  <si>
-    <t>e_w202980838*</t>
-  </si>
-  <si>
-    <t>p_w209806624</t>
-  </si>
-  <si>
-    <t>e_w209806624*</t>
-  </si>
-  <si>
-    <t>p_w209826798</t>
-  </si>
-  <si>
-    <t>e_w209826798*</t>
-  </si>
-  <si>
-    <t>p_w245128370</t>
-  </si>
-  <si>
-    <t>e_w245128370*</t>
-  </si>
-  <si>
-    <t>p_w247861059</t>
-  </si>
-  <si>
-    <t>e_w247861059*</t>
-  </si>
-  <si>
-    <t>p_w248385304</t>
-  </si>
-  <si>
-    <t>e_w248385304*</t>
-  </si>
-  <si>
-    <t>p_w274106872</t>
-  </si>
-  <si>
-    <t>e_w274106872*</t>
-  </si>
-  <si>
-    <t>p_w293597835</t>
-  </si>
-  <si>
-    <t>e_w293597835*</t>
-  </si>
-  <si>
-    <t>p_w311103617</t>
-  </si>
-  <si>
-    <t>e_w311103617*</t>
-  </si>
-  <si>
-    <t>p_w311118424</t>
-  </si>
-  <si>
-    <t>e_w311118424*</t>
-  </si>
-  <si>
-    <t>p_w311176519</t>
-  </si>
-  <si>
-    <t>e_w311176519*</t>
-  </si>
-  <si>
-    <t>p_w311571096</t>
-  </si>
-  <si>
-    <t>e_w311571096*</t>
-  </si>
-  <si>
-    <t>p_w311933111</t>
-  </si>
-  <si>
-    <t>e_w311933111*</t>
-  </si>
-  <si>
-    <t>p_w311954703</t>
-  </si>
-  <si>
-    <t>e_w311954703*</t>
-  </si>
-  <si>
-    <t>p_w1246177377</t>
-  </si>
-  <si>
-    <t>e_w1246177377*</t>
-  </si>
-  <si>
-    <t>p_w315477169</t>
-  </si>
-  <si>
-    <t>e_w315477169*</t>
-  </si>
-  <si>
-    <t>p_w315823978</t>
-  </si>
-  <si>
-    <t>e_w315823978*</t>
-  </si>
-  <si>
-    <t>p_w315824842</t>
-  </si>
-  <si>
-    <t>e_w315824842*</t>
-  </si>
-  <si>
-    <t>p_w316463122</t>
-  </si>
-  <si>
-    <t>e_w316463122*</t>
-  </si>
-  <si>
-    <t>p_w318050929</t>
-  </si>
-  <si>
-    <t>e_w318050929*</t>
-  </si>
-  <si>
-    <t>p_w318090288</t>
-  </si>
-  <si>
-    <t>e_w318090288*</t>
-  </si>
-  <si>
-    <t>p_w319423421</t>
-  </si>
-  <si>
-    <t>e_w319423421*</t>
-  </si>
-  <si>
-    <t>p_w323266562</t>
-  </si>
-  <si>
-    <t>e_w323266562*</t>
-  </si>
-  <si>
-    <t>p_w328548895</t>
-  </si>
-  <si>
-    <t>e_w328548895*</t>
-  </si>
-  <si>
-    <t>p_w331275940</t>
-  </si>
-  <si>
-    <t>e_w331275940*</t>
-  </si>
-  <si>
-    <t>p_w342204888</t>
-  </si>
-  <si>
-    <t>e_w342204888*</t>
-  </si>
-  <si>
-    <t>p_w352619220</t>
-  </si>
-  <si>
-    <t>e_w352619220*</t>
-  </si>
-  <si>
-    <t>p_w353914761</t>
-  </si>
-  <si>
-    <t>e_w353914761*</t>
-  </si>
-  <si>
-    <t>p_w353914865</t>
-  </si>
-  <si>
-    <t>e_w353914865*</t>
-  </si>
-  <si>
-    <t>p_w354062412</t>
-  </si>
-  <si>
-    <t>e_w354062412*</t>
-  </si>
-  <si>
-    <t>p_w355560316</t>
-  </si>
-  <si>
-    <t>e_w355560316*</t>
-  </si>
-  <si>
-    <t>p_w357515226</t>
-  </si>
-  <si>
-    <t>e_w357515226*</t>
-  </si>
-  <si>
-    <t>p_w360424761</t>
-  </si>
-  <si>
-    <t>e_w360424761*</t>
-  </si>
-  <si>
-    <t>p_w369866141</t>
-  </si>
-  <si>
-    <t>e_w369866141*</t>
-  </si>
-  <si>
-    <t>p_w372701897</t>
-  </si>
-  <si>
-    <t>e_w372701897*</t>
-  </si>
-  <si>
-    <t>p_w386018740</t>
-  </si>
-  <si>
-    <t>e_w386018740*</t>
-  </si>
-  <si>
-    <t>p_w386153973</t>
-  </si>
-  <si>
-    <t>e_w386153973*</t>
-  </si>
-  <si>
-    <t>p_w408924420</t>
-  </si>
-  <si>
-    <t>e_w408924420*</t>
-  </si>
-  <si>
-    <t>p_w408924427</t>
-  </si>
-  <si>
-    <t>e_w408924427*</t>
-  </si>
-  <si>
-    <t>p_w409112085</t>
-  </si>
-  <si>
-    <t>e_w409112085*</t>
-  </si>
-  <si>
-    <t>p_w409158116</t>
-  </si>
-  <si>
-    <t>e_w409158116*</t>
-  </si>
-  <si>
-    <t>p_w409798382</t>
-  </si>
-  <si>
-    <t>e_w409798382*</t>
-  </si>
-  <si>
-    <t>p_w417569420</t>
-  </si>
-  <si>
-    <t>e_w417569420*</t>
-  </si>
-  <si>
-    <t>p_w420797421</t>
-  </si>
-  <si>
-    <t>e_w420797421*</t>
-  </si>
-  <si>
-    <t>p_w422204218</t>
-  </si>
-  <si>
-    <t>e_w422204218*</t>
-  </si>
-  <si>
-    <t>p_w423166766</t>
-  </si>
-  <si>
-    <t>e_w423166766*</t>
-  </si>
-  <si>
-    <t>p_w423702239</t>
-  </si>
-  <si>
-    <t>e_w423702239*</t>
-  </si>
-  <si>
-    <t>p_w425101516</t>
-  </si>
-  <si>
-    <t>e_w425101516*</t>
-  </si>
-  <si>
-    <t>p_w425401901</t>
-  </si>
-  <si>
-    <t>e_w425401901*</t>
-  </si>
-  <si>
-    <t>p_w429459345</t>
-  </si>
-  <si>
-    <t>e_w429459345*</t>
-  </si>
-  <si>
-    <t>p_w453513742</t>
-  </si>
-  <si>
-    <t>e_w453513742*</t>
-  </si>
-  <si>
-    <t>p_w466424134</t>
-  </si>
-  <si>
-    <t>e_w466424134*</t>
-  </si>
-  <si>
-    <t>p_w801704865</t>
-  </si>
-  <si>
-    <t>e_w801704865*</t>
-  </si>
-  <si>
-    <t>p_w473902678</t>
-  </si>
-  <si>
-    <t>e_w473902678*</t>
-  </si>
-  <si>
-    <t>p_w477691456</t>
-  </si>
-  <si>
-    <t>e_w477691456*</t>
-  </si>
-  <si>
-    <t>p_w506461670</t>
-  </si>
-  <si>
-    <t>e_w506461670*</t>
-  </si>
-  <si>
-    <t>p_w514344408</t>
-  </si>
-  <si>
-    <t>e_w514344408*</t>
-  </si>
-  <si>
-    <t>p_w521570801</t>
-  </si>
-  <si>
-    <t>e_w521570801*</t>
-  </si>
-  <si>
-    <t>p_w545571850</t>
-  </si>
-  <si>
-    <t>e_w545571850*</t>
-  </si>
-  <si>
-    <t>p_w551402699</t>
-  </si>
-  <si>
-    <t>e_w551402699*</t>
-  </si>
-  <si>
-    <t>p_w607439318</t>
-  </si>
-  <si>
-    <t>e_w607439318*</t>
-  </si>
-  <si>
-    <t>p_w608461884</t>
-  </si>
-  <si>
-    <t>e_w608461884*</t>
-  </si>
-  <si>
-    <t>p_w631917408</t>
-  </si>
-  <si>
-    <t>e_w631917408*</t>
-  </si>
-  <si>
-    <t>p_w654736039</t>
-  </si>
-  <si>
-    <t>e_w654736039*</t>
-  </si>
-  <si>
-    <t>p_w655683221</t>
-  </si>
-  <si>
-    <t>e_w655683221*</t>
-  </si>
-  <si>
-    <t>p_w686891085</t>
-  </si>
-  <si>
-    <t>e_w686891085*</t>
-  </si>
-  <si>
-    <t>p_w688672711</t>
-  </si>
-  <si>
-    <t>e_w688672711*</t>
-  </si>
-  <si>
-    <t>p_w688672798</t>
-  </si>
-  <si>
-    <t>e_w688672798*</t>
-  </si>
-  <si>
-    <t>p_w698045832</t>
-  </si>
-  <si>
-    <t>e_w698045832*</t>
-  </si>
-  <si>
-    <t>p_w751947947</t>
-  </si>
-  <si>
-    <t>e_w751947947*</t>
-  </si>
-  <si>
-    <t>p_w759521252</t>
-  </si>
-  <si>
-    <t>e_w759521252*</t>
-  </si>
-  <si>
-    <t>p_w781425567</t>
-  </si>
-  <si>
-    <t>e_w781425567*</t>
-  </si>
-  <si>
-    <t>p_w793144832</t>
-  </si>
-  <si>
-    <t>e_w793144832*</t>
-  </si>
-  <si>
-    <t>p_w840600239</t>
-  </si>
-  <si>
-    <t>e_w840600239*</t>
-  </si>
-  <si>
-    <t>p_w910151268</t>
-  </si>
-  <si>
-    <t>e_w910151268*</t>
-  </si>
-  <si>
-    <t>p_w923365745</t>
-  </si>
-  <si>
-    <t>e_w923365745*</t>
-  </si>
-  <si>
-    <t>p_w1001700959</t>
-  </si>
-  <si>
-    <t>e_w1001700959*</t>
-  </si>
-  <si>
-    <t>p_w1074489047</t>
-  </si>
-  <si>
-    <t>e_w1074489047*</t>
-  </si>
-  <si>
-    <t>p_w1077819664</t>
-  </si>
-  <si>
-    <t>e_w1077819664*</t>
-  </si>
-  <si>
-    <t>p_w1078426593</t>
-  </si>
-  <si>
-    <t>e_w1078426593*</t>
-  </si>
-  <si>
-    <t>p_w1127651311</t>
-  </si>
-  <si>
-    <t>e_w1127651311*</t>
-  </si>
-  <si>
-    <t>p_w1143180503</t>
-  </si>
-  <si>
-    <t>e_w1143180503*</t>
-  </si>
-  <si>
-    <t>p_w1206014676</t>
-  </si>
-  <si>
-    <t>e_w1206014676*</t>
-  </si>
-  <si>
-    <t>p_w1207477934</t>
-  </si>
-  <si>
-    <t>e_w1207477934*</t>
-  </si>
-  <si>
-    <t>p_w1329624553</t>
-  </si>
-  <si>
-    <t>e_w1329624553*</t>
-  </si>
-  <si>
-    <t>p_w1336628403</t>
-  </si>
-  <si>
-    <t>e_w1336628403*</t>
-  </si>
-  <si>
-    <t>p_w1341291951</t>
-  </si>
-  <si>
-    <t>e_w1341291951*</t>
-  </si>
-  <si>
-    <t>p_w1415199647</t>
-  </si>
-  <si>
-    <t>e_w1415199647*</t>
-  </si>
-  <si>
-    <t>p_IN532</t>
-  </si>
-  <si>
-    <t>e_IN532*</t>
-  </si>
-  <si>
-    <t>p_IN10</t>
-  </si>
-  <si>
-    <t>e_IN10*</t>
-  </si>
-  <si>
-    <t>p_IN372</t>
-  </si>
-  <si>
-    <t>e_IN372*</t>
-  </si>
-  <si>
-    <t>p_IN328</t>
-  </si>
-  <si>
-    <t>e_IN328*</t>
-  </si>
-  <si>
-    <t>p_IN373</t>
-  </si>
-  <si>
-    <t>e_IN373*</t>
-  </si>
-  <si>
-    <t>p_IN367</t>
-  </si>
-  <si>
-    <t>e_IN367*</t>
-  </si>
-  <si>
-    <t>p_IN289</t>
-  </si>
-  <si>
-    <t>e_IN289*</t>
-  </si>
-  <si>
-    <t>p_IN323</t>
-  </si>
-  <si>
-    <t>e_IN323*</t>
-  </si>
-  <si>
-    <t>p_IN365</t>
-  </si>
-  <si>
-    <t>e_IN365*</t>
-  </si>
-  <si>
-    <t>p_IN346</t>
-  </si>
-  <si>
-    <t>e_IN346*</t>
-  </si>
-  <si>
-    <t>p_IN350</t>
-  </si>
-  <si>
-    <t>e_IN350*</t>
-  </si>
-  <si>
-    <t>p_IN370</t>
-  </si>
-  <si>
-    <t>e_IN370*</t>
-  </si>
-  <si>
-    <t>p_IN380</t>
-  </si>
-  <si>
-    <t>e_IN380*</t>
-  </si>
-  <si>
-    <t>p_IN388</t>
-  </si>
-  <si>
-    <t>e_IN388*</t>
-  </si>
-  <si>
-    <t>p_IN343</t>
-  </si>
-  <si>
-    <t>e_IN343*</t>
-  </si>
-  <si>
-    <t>p_IN136</t>
-  </si>
-  <si>
-    <t>e_IN136*</t>
-  </si>
-  <si>
-    <t>p_IN473</t>
-  </si>
-  <si>
-    <t>e_IN473*</t>
-  </si>
-  <si>
-    <t>p_IN244</t>
-  </si>
-  <si>
-    <t>e_IN244*</t>
-  </si>
-  <si>
-    <t>p_IN489</t>
-  </si>
-  <si>
-    <t>e_IN489*</t>
-  </si>
-  <si>
-    <t>p_IN321</t>
-  </si>
-  <si>
-    <t>e_IN321*</t>
-  </si>
-  <si>
-    <t>p_IN276</t>
-  </si>
-  <si>
-    <t>e_IN276*</t>
-  </si>
-  <si>
-    <t>p_IN327</t>
-  </si>
-  <si>
-    <t>e_IN327*</t>
-  </si>
-  <si>
-    <t>p_IN288</t>
-  </si>
-  <si>
-    <t>e_IN288*</t>
-  </si>
-  <si>
-    <t>p_IN329</t>
-  </si>
-  <si>
-    <t>e_IN329*</t>
-  </si>
-  <si>
-    <t>p_IN270</t>
-  </si>
-  <si>
-    <t>e_IN270*</t>
-  </si>
-  <si>
-    <t>p_IN264</t>
-  </si>
-  <si>
-    <t>e_IN264*</t>
-  </si>
-  <si>
-    <t>p_IN272</t>
-  </si>
-  <si>
-    <t>e_IN272*</t>
-  </si>
-  <si>
-    <t>p_IN278</t>
-  </si>
-  <si>
-    <t>e_IN278*</t>
-  </si>
-  <si>
-    <t>p_IN612</t>
-  </si>
-  <si>
-    <t>e_IN612*</t>
-  </si>
-  <si>
-    <t>p_IN394</t>
-  </si>
-  <si>
-    <t>e_IN394*</t>
-  </si>
-  <si>
-    <t>p_IN387</t>
-  </si>
-  <si>
-    <t>e_IN387*</t>
-  </si>
-  <si>
-    <t>p_IN382</t>
-  </si>
-  <si>
-    <t>e_IN382*</t>
-  </si>
-  <si>
-    <t>p_IN399</t>
-  </si>
-  <si>
-    <t>e_IN399*</t>
-  </si>
-  <si>
-    <t>p_IN403</t>
-  </si>
-  <si>
-    <t>e_IN403*</t>
-  </si>
-  <si>
-    <t>p_IN405</t>
-  </si>
-  <si>
-    <t>e_IN405*</t>
-  </si>
-  <si>
-    <t>p_IN393</t>
-  </si>
-  <si>
-    <t>e_IN393*</t>
-  </si>
-  <si>
-    <t>p_IN392</t>
-  </si>
-  <si>
-    <t>e_IN392*</t>
-  </si>
-  <si>
-    <t>p_IN390</t>
-  </si>
-  <si>
-    <t>e_IN390*</t>
-  </si>
-  <si>
-    <t>p_IN384</t>
-  </si>
-  <si>
-    <t>e_IN384*</t>
-  </si>
-  <si>
-    <t>p_IN381</t>
-  </si>
-  <si>
-    <t>e_IN381*</t>
-  </si>
-  <si>
-    <t>p_IN395</t>
-  </si>
-  <si>
-    <t>e_IN395*</t>
-  </si>
-  <si>
-    <t>p_IN376</t>
-  </si>
-  <si>
-    <t>e_IN376*</t>
-  </si>
-  <si>
-    <t>p_IN402</t>
-  </si>
-  <si>
-    <t>e_IN402*</t>
-  </si>
-  <si>
-    <t>p_IN397</t>
-  </si>
-  <si>
-    <t>e_IN397*</t>
-  </si>
-  <si>
-    <t>p_IN404</t>
-  </si>
-  <si>
-    <t>e_IN404*</t>
-  </si>
-  <si>
-    <t>p_IN412</t>
-  </si>
-  <si>
-    <t>e_IN412*</t>
-  </si>
-  <si>
-    <t>p_IN247</t>
-  </si>
-  <si>
-    <t>e_IN247*</t>
-  </si>
-  <si>
-    <t>p_IN250</t>
-  </si>
-  <si>
-    <t>e_IN250*</t>
-  </si>
-  <si>
-    <t>p_IN249</t>
-  </si>
-  <si>
-    <t>e_IN249*</t>
-  </si>
-  <si>
-    <t>p_IN246</t>
-  </si>
-  <si>
-    <t>e_IN246*</t>
-  </si>
-  <si>
-    <t>p_IN490</t>
-  </si>
-  <si>
-    <t>e_IN490*</t>
-  </si>
-  <si>
-    <t>p_IN488</t>
-  </si>
-  <si>
-    <t>e_IN488*</t>
-  </si>
-  <si>
-    <t>p_IN583</t>
-  </si>
-  <si>
-    <t>e_IN583*</t>
-  </si>
-  <si>
-    <t>p_IN586</t>
-  </si>
-  <si>
-    <t>e_IN586*</t>
-  </si>
-  <si>
-    <t>p_IN555</t>
-  </si>
-  <si>
-    <t>e_IN555*</t>
-  </si>
-  <si>
-    <t>p_IN293</t>
-  </si>
-  <si>
-    <t>e_IN293*</t>
-  </si>
-  <si>
-    <t>p_IN230</t>
-  </si>
-  <si>
-    <t>e_IN230*</t>
-  </si>
-  <si>
-    <t>p_IN233</t>
-  </si>
-  <si>
-    <t>e_IN233*</t>
-  </si>
-  <si>
-    <t>p_IN400</t>
-  </si>
-  <si>
-    <t>e_IN400*</t>
-  </si>
-  <si>
-    <t>p_IN396</t>
-  </si>
-  <si>
-    <t>e_IN396*</t>
-  </si>
-  <si>
-    <t>p_IN391</t>
-  </si>
-  <si>
-    <t>e_IN391*</t>
-  </si>
-  <si>
-    <t>p_IN205</t>
-  </si>
-  <si>
-    <t>e_IN205*</t>
-  </si>
-  <si>
-    <t>p_IN206</t>
-  </si>
-  <si>
-    <t>e_IN206*</t>
-  </si>
-  <si>
-    <t>p_IN202</t>
-  </si>
-  <si>
-    <t>e_IN202*</t>
-  </si>
-  <si>
-    <t>p_IN101</t>
-  </si>
-  <si>
-    <t>e_IN101*</t>
-  </si>
-  <si>
-    <t>p_IN105</t>
-  </si>
-  <si>
-    <t>e_IN105*</t>
-  </si>
-  <si>
-    <t>p_IN100</t>
-  </si>
-  <si>
-    <t>e_IN100*</t>
-  </si>
-  <si>
-    <t>p_IN85</t>
-  </si>
-  <si>
-    <t>e_IN85*</t>
-  </si>
-  <si>
-    <t>p_IN225</t>
-  </si>
-  <si>
-    <t>e_IN225*</t>
-  </si>
-  <si>
-    <t>p_IN196</t>
-  </si>
-  <si>
-    <t>e_IN196*</t>
-  </si>
-  <si>
-    <t>p_IN229</t>
-  </si>
-  <si>
-    <t>e_IN229*</t>
-  </si>
-  <si>
-    <t>p_IN609</t>
-  </si>
-  <si>
-    <t>e_IN609*</t>
-  </si>
-  <si>
-    <t>p_IN610</t>
-  </si>
-  <si>
-    <t>e_IN610*</t>
-  </si>
-  <si>
-    <t>p_IN607</t>
-  </si>
-  <si>
-    <t>e_IN607*</t>
-  </si>
-  <si>
-    <t>p_IN617</t>
-  </si>
-  <si>
-    <t>e_IN617*</t>
-  </si>
-  <si>
-    <t>p_IN306</t>
-  </si>
-  <si>
-    <t>e_IN306*</t>
-  </si>
-  <si>
-    <t>p_IN300</t>
-  </si>
-  <si>
-    <t>e_IN300*</t>
-  </si>
-  <si>
-    <t>p_IN142</t>
-  </si>
-  <si>
-    <t>e_IN142*</t>
-  </si>
-  <si>
-    <t>p_IN200</t>
-  </si>
-  <si>
-    <t>e_IN200*</t>
-  </si>
-  <si>
-    <t>p_IN171</t>
-  </si>
-  <si>
-    <t>e_IN171*</t>
-  </si>
-  <si>
-    <t>p_IN541</t>
-  </si>
-  <si>
-    <t>e_IN541*</t>
-  </si>
-  <si>
-    <t>p_IN642</t>
-  </si>
-  <si>
-    <t>e_IN642*</t>
-  </si>
-  <si>
-    <t>p_IN284</t>
-  </si>
-  <si>
-    <t>e_IN284*</t>
-  </si>
-  <si>
-    <t>p_IN239</t>
-  </si>
-  <si>
-    <t>e_IN239*</t>
-  </si>
-  <si>
-    <t>p_IN282</t>
-  </si>
-  <si>
-    <t>e_IN282*</t>
-  </si>
-  <si>
-    <t>p_IN292</t>
-  </si>
-  <si>
-    <t>e_IN292*</t>
-  </si>
-  <si>
-    <t>p_IN295</t>
-  </si>
-  <si>
-    <t>e_IN295*</t>
-  </si>
-  <si>
-    <t>p_IN529</t>
-  </si>
-  <si>
-    <t>e_IN529*</t>
-  </si>
-  <si>
-    <t>p_IN457</t>
-  </si>
-  <si>
-    <t>e_IN457*</t>
-  </si>
-  <si>
-    <t>p_IN540</t>
-  </si>
-  <si>
-    <t>e_IN540*</t>
-  </si>
-  <si>
-    <t>p_IN240</t>
-  </si>
-  <si>
-    <t>e_IN240*</t>
-  </si>
-  <si>
-    <t>p_IN280</t>
-  </si>
-  <si>
-    <t>e_IN280*</t>
-  </si>
-  <si>
-    <t>p_IN279</t>
-  </si>
-  <si>
-    <t>e_IN279*</t>
-  </si>
-  <si>
-    <t>p_IN539</t>
-  </si>
-  <si>
-    <t>e_IN539*</t>
-  </si>
-  <si>
-    <t>p_IN537</t>
-  </si>
-  <si>
-    <t>e_IN537*</t>
-  </si>
-  <si>
-    <t>p_IN476</t>
-  </si>
-  <si>
-    <t>e_IN476*</t>
-  </si>
-  <si>
-    <t>p_IN439</t>
-  </si>
-  <si>
-    <t>e_IN439*</t>
-  </si>
-  <si>
-    <t>p_IN548</t>
-  </si>
-  <si>
-    <t>e_IN548*</t>
-  </si>
-  <si>
-    <t>p_IN416</t>
-  </si>
-  <si>
-    <t>e_IN416*</t>
-  </si>
-  <si>
-    <t>p_IN413</t>
-  </si>
-  <si>
-    <t>e_IN413*</t>
-  </si>
-  <si>
-    <t>p_IN742</t>
-  </si>
-  <si>
-    <t>e_IN742*</t>
-  </si>
-  <si>
-    <t>p_IN749</t>
-  </si>
-  <si>
-    <t>e_IN749*</t>
-  </si>
-  <si>
-    <t>p_IN684</t>
-  </si>
-  <si>
-    <t>e_IN684*</t>
-  </si>
-  <si>
-    <t>p_IN135</t>
-  </si>
-  <si>
-    <t>e_IN135*</t>
-  </si>
-  <si>
-    <t>p_IN685</t>
-  </si>
-  <si>
-    <t>e_IN685*</t>
-  </si>
-  <si>
-    <t>p_IN159</t>
-  </si>
-  <si>
-    <t>e_IN159*</t>
-  </si>
-  <si>
-    <t>p_IN161</t>
-  </si>
-  <si>
-    <t>e_IN161*</t>
-  </si>
-  <si>
-    <t>p_IN164</t>
-  </si>
-  <si>
-    <t>e_IN164*</t>
-  </si>
-  <si>
-    <t>p_IN163</t>
-  </si>
-  <si>
-    <t>e_IN163*</t>
-  </si>
-  <si>
-    <t>p_IN187</t>
-  </si>
-  <si>
-    <t>e_IN187*</t>
-  </si>
-  <si>
-    <t>p_IN218</t>
-  </si>
-  <si>
-    <t>e_IN218*</t>
-  </si>
-  <si>
-    <t>p_IN197</t>
-  </si>
-  <si>
-    <t>e_IN197*</t>
-  </si>
-  <si>
-    <t>p_IN807</t>
-  </si>
-  <si>
-    <t>e_IN807*</t>
-  </si>
-  <si>
-    <t>p_IN801</t>
-  </si>
-  <si>
-    <t>e_IN801*</t>
-  </si>
-  <si>
-    <t>p_IN803</t>
-  </si>
-  <si>
-    <t>e_IN803*</t>
-  </si>
-  <si>
-    <t>p_IN798</t>
-  </si>
-  <si>
-    <t>e_IN798*</t>
-  </si>
-  <si>
-    <t>p_IN137</t>
-  </si>
-  <si>
-    <t>e_IN137*</t>
-  </si>
-  <si>
-    <t>p_IN139</t>
-  </si>
-  <si>
-    <t>e_IN139*</t>
-  </si>
-  <si>
-    <t>p_IN148</t>
-  </si>
-  <si>
-    <t>e_IN148*</t>
-  </si>
-  <si>
-    <t>p_IN191</t>
-  </si>
-  <si>
-    <t>e_IN191*</t>
-  </si>
-  <si>
-    <t>p_IN73</t>
-  </si>
-  <si>
-    <t>e_IN73*</t>
-  </si>
-  <si>
-    <t>p_IN42</t>
-  </si>
-  <si>
-    <t>e_IN42*</t>
-  </si>
-  <si>
-    <t>p_IN108</t>
-  </si>
-  <si>
-    <t>e_IN108*</t>
-  </si>
-  <si>
-    <t>p_w492377703</t>
-  </si>
-  <si>
-    <t>e_w492377703*</t>
-  </si>
-  <si>
-    <t>p_IN375</t>
-  </si>
-  <si>
-    <t>e_IN375*</t>
-  </si>
-  <si>
-    <t>p_IN107</t>
-  </si>
-  <si>
-    <t>e_IN107*</t>
-  </si>
-  <si>
-    <t>p_IN307</t>
-  </si>
-  <si>
-    <t>e_IN307*</t>
-  </si>
-  <si>
-    <t>p_IN298</t>
-  </si>
-  <si>
-    <t>e_IN298*</t>
-  </si>
-  <si>
-    <t>p_IN275</t>
-  </si>
-  <si>
-    <t>e_IN275*</t>
-  </si>
-  <si>
-    <t>p_IN268</t>
-  </si>
-  <si>
-    <t>e_IN268*</t>
-  </si>
-  <si>
-    <t>p_IN253</t>
-  </si>
-  <si>
-    <t>e_IN253*</t>
-  </si>
-  <si>
-    <t>p_IN255</t>
-  </si>
-  <si>
-    <t>e_IN255*</t>
-  </si>
-  <si>
-    <t>p_IN222</t>
-  </si>
-  <si>
-    <t>e_IN222*</t>
-  </si>
-  <si>
-    <t>p_IN201</t>
-  </si>
-  <si>
-    <t>e_IN201*</t>
-  </si>
-  <si>
-    <t>p_IN190</t>
-  </si>
-  <si>
-    <t>e_IN190*</t>
-  </si>
-  <si>
-    <t>p_IN178</t>
-  </si>
-  <si>
-    <t>e_IN178*</t>
-  </si>
-  <si>
-    <t>p_IN254</t>
-  </si>
-  <si>
-    <t>e_IN254*</t>
-  </si>
-  <si>
-    <t>p_IN116</t>
-  </si>
-  <si>
-    <t>e_IN116*</t>
-  </si>
-  <si>
-    <t>p_IN126</t>
-  </si>
-  <si>
-    <t>e_IN126*</t>
-  </si>
-  <si>
-    <t>p_IN123</t>
-  </si>
-  <si>
-    <t>e_IN123*</t>
-  </si>
-  <si>
-    <t>p_IN120</t>
-  </si>
-  <si>
-    <t>e_IN120*</t>
-  </si>
-  <si>
-    <t>p_IN351</t>
-  </si>
-  <si>
-    <t>e_IN351*</t>
-  </si>
-  <si>
-    <t>p_IN243</t>
-  </si>
-  <si>
-    <t>e_IN243*</t>
-  </si>
-  <si>
-    <t>p_IN486</t>
-  </si>
-  <si>
-    <t>e_IN486*</t>
-  </si>
-  <si>
-    <t>p_IN277</t>
-  </si>
-  <si>
-    <t>e_IN277*</t>
-  </si>
-  <si>
-    <t>p_IN401</t>
-  </si>
-  <si>
-    <t>e_IN401*</t>
-  </si>
-  <si>
-    <t>p_IN535</t>
-  </si>
-  <si>
-    <t>e_IN535*</t>
-  </si>
-  <si>
-    <t>p_IN578</t>
-  </si>
-  <si>
-    <t>e_IN578*</t>
-  </si>
-  <si>
-    <t>p_IN283</t>
-  </si>
-  <si>
-    <t>e_IN283*</t>
-  </si>
-  <si>
-    <t>p_IN599</t>
-  </si>
-  <si>
-    <t>e_IN599*</t>
-  </si>
-  <si>
-    <t>p_IN203</t>
-  </si>
-  <si>
-    <t>e_IN203*</t>
-  </si>
-  <si>
-    <t>p_IN180</t>
-  </si>
-  <si>
-    <t>e_IN180*</t>
-  </si>
-  <si>
-    <t>p_IN104</t>
-  </si>
-  <si>
-    <t>e_IN104*</t>
-  </si>
-  <si>
-    <t>p_IN659</t>
-  </si>
-  <si>
-    <t>e_IN659*</t>
-  </si>
-  <si>
-    <t>p_IN160</t>
-  </si>
-  <si>
-    <t>e_IN160*</t>
-  </si>
-  <si>
-    <t>p_IN174</t>
-  </si>
-  <si>
-    <t>e_IN174*</t>
-  </si>
-  <si>
-    <t>p_IN312</t>
-  </si>
-  <si>
-    <t>e_IN312*</t>
-  </si>
-  <si>
-    <t>p_IN167</t>
-  </si>
-  <si>
-    <t>e_IN167*</t>
-  </si>
-  <si>
-    <t>p_w196563905</t>
-  </si>
-  <si>
-    <t>e_w196563905*</t>
-  </si>
-  <si>
-    <t>p_IN748</t>
-  </si>
-  <si>
-    <t>e_IN748*</t>
-  </si>
-  <si>
-    <t>p_IN267</t>
-  </si>
-  <si>
-    <t>e_IN267*</t>
-  </si>
-  <si>
-    <t>p_IN215</t>
-  </si>
-  <si>
-    <t>e_IN215*</t>
-  </si>
-  <si>
-    <t>p_IN199</t>
-  </si>
-  <si>
-    <t>e_IN199*</t>
-  </si>
-  <si>
-    <t>p_IN194</t>
-  </si>
-  <si>
-    <t>e_IN194*</t>
-  </si>
-  <si>
-    <t>p_IN809</t>
-  </si>
-  <si>
-    <t>e_IN809*</t>
-  </si>
-  <si>
-    <t>p_IN808</t>
-  </si>
-  <si>
-    <t>e_IN808*</t>
-  </si>
-  <si>
-    <t>p_IN806</t>
-  </si>
-  <si>
-    <t>e_IN806*</t>
-  </si>
-  <si>
-    <t>p_IN146</t>
-  </si>
-  <si>
-    <t>e_IN146*</t>
-  </si>
-  <si>
-    <t>p_IN138</t>
-  </si>
-  <si>
-    <t>e_IN138*</t>
-  </si>
-  <si>
-    <t>p_IN140</t>
-  </si>
-  <si>
-    <t>e_IN140*</t>
-  </si>
-  <si>
-    <t>p_IN94</t>
-  </si>
-  <si>
-    <t>e_IN94*</t>
-  </si>
-  <si>
-    <t>p_IN302</t>
-  </si>
-  <si>
-    <t>e_IN302*</t>
-  </si>
-  <si>
-    <t>p_IN269</t>
-  </si>
-  <si>
-    <t>e_IN269*</t>
-  </si>
-  <si>
-    <t>p_IN258</t>
-  </si>
-  <si>
-    <t>e_IN258*</t>
-  </si>
-  <si>
-    <t>p_IN232</t>
-  </si>
-  <si>
-    <t>e_IN232*</t>
-  </si>
-  <si>
-    <t>p_IN257</t>
-  </si>
-  <si>
-    <t>e_IN257*</t>
-  </si>
-  <si>
-    <t>p_IN217</t>
-  </si>
-  <si>
-    <t>e_IN217*</t>
-  </si>
-  <si>
-    <t>p_IN198</t>
-  </si>
-  <si>
-    <t>e_IN198*</t>
-  </si>
-  <si>
-    <t>p_IN183</t>
-  </si>
-  <si>
-    <t>e_IN183*</t>
-  </si>
-  <si>
-    <t>p_IN175</t>
-  </si>
-  <si>
-    <t>e_IN175*</t>
-  </si>
-  <si>
-    <t>p_IN128</t>
-  </si>
-  <si>
-    <t>e_IN128*</t>
-  </si>
-  <si>
-    <t>p_IN125</t>
-  </si>
-  <si>
-    <t>e_IN125*</t>
-  </si>
-  <si>
-    <t>p_IN121</t>
-  </si>
-  <si>
-    <t>e_IN121*</t>
-  </si>
-  <si>
-    <t>p_w116541259</t>
-  </si>
-  <si>
-    <t>e_w116541259*</t>
-  </si>
-  <si>
-    <t>p_w203673991</t>
-  </si>
-  <si>
-    <t>e_w203673991*</t>
-  </si>
-  <si>
-    <t>p_w239498664</t>
-  </si>
-  <si>
-    <t>e_w239498664*</t>
-  </si>
-  <si>
-    <t>p_w374367235</t>
-  </si>
-  <si>
-    <t>e_w374367235*</t>
-  </si>
-  <si>
-    <t>p_w375084335</t>
-  </si>
-  <si>
-    <t>e_w375084335*</t>
-  </si>
-  <si>
-    <t>p_w375941438</t>
-  </si>
-  <si>
-    <t>e_w375941438*</t>
-  </si>
-  <si>
-    <t>p_w439006823</t>
-  </si>
-  <si>
-    <t>e_w439006823*</t>
-  </si>
-  <si>
-    <t>p_w465787206</t>
-  </si>
-  <si>
-    <t>e_w465787206*</t>
-  </si>
-  <si>
-    <t>p_w610646823</t>
-  </si>
-  <si>
-    <t>e_w610646823*</t>
-  </si>
-  <si>
-    <t>p_w1072445901</t>
-  </si>
-  <si>
-    <t>e_w1072445901*</t>
-  </si>
-  <si>
-    <t>p_w1099365556</t>
-  </si>
-  <si>
-    <t>e_w1099365556*</t>
-  </si>
-  <si>
-    <t>p_w1099365579</t>
-  </si>
-  <si>
-    <t>e_w1099365579*</t>
-  </si>
-  <si>
-    <t>p_w1265489491</t>
-  </si>
-  <si>
-    <t>e_w1265489491*</t>
-  </si>
-  <si>
-    <t>p_w1265496720</t>
-  </si>
-  <si>
-    <t>e_w1265496720*</t>
-  </si>
-  <si>
-    <t>p_IN177</t>
-  </si>
-  <si>
-    <t>e_IN177*</t>
-  </si>
-  <si>
-    <t>p_IN440</t>
-  </si>
-  <si>
-    <t>e_IN440*</t>
-  </si>
-  <si>
-    <t>p_IN235</t>
-  </si>
-  <si>
-    <t>e_IN235*</t>
-  </si>
-  <si>
-    <t>p_IN265</t>
-  </si>
-  <si>
-    <t>e_IN265*</t>
-  </si>
-  <si>
-    <t>p_IN145</t>
-  </si>
-  <si>
-    <t>e_IN145*</t>
-  </si>
-  <si>
-    <t>p_IN176</t>
-  </si>
-  <si>
-    <t>e_IN176*</t>
-  </si>
-  <si>
-    <t>p_IN260</t>
-  </si>
-  <si>
-    <t>e_IN260*</t>
-  </si>
-  <si>
-    <t>p_IN386</t>
-  </si>
-  <si>
-    <t>e_IN386*</t>
-  </si>
-  <si>
-    <t>p_w92360278</t>
-  </si>
-  <si>
-    <t>e_w92360278*</t>
-  </si>
-  <si>
-    <t>p_w92994753</t>
-  </si>
-  <si>
-    <t>e_w92994753*</t>
-  </si>
-  <si>
-    <t>p_w93160503</t>
-  </si>
-  <si>
-    <t>e_w93160503*</t>
-  </si>
-  <si>
-    <t>p_w94199110</t>
-  </si>
-  <si>
-    <t>e_w94199110*</t>
-  </si>
-  <si>
-    <t>p_w96821783</t>
-  </si>
-  <si>
-    <t>e_w96821783*</t>
-  </si>
-  <si>
-    <t>p_w118228036</t>
-  </si>
-  <si>
-    <t>e_w118228036*</t>
-  </si>
-  <si>
-    <t>p_w149822703</t>
-  </si>
-  <si>
-    <t>e_w149822703*</t>
-  </si>
-  <si>
-    <t>p_w166692103</t>
-  </si>
-  <si>
-    <t>e_w166692103*</t>
-  </si>
-  <si>
-    <t>p_w205942950</t>
-  </si>
-  <si>
-    <t>e_w205942950*</t>
-  </si>
-  <si>
-    <t>p_w209806650</t>
-  </si>
-  <si>
-    <t>e_w209806650*</t>
-  </si>
-  <si>
-    <t>p_w324059200</t>
-  </si>
-  <si>
-    <t>e_w324059200*</t>
-  </si>
-  <si>
-    <t>p_w324064297</t>
-  </si>
-  <si>
-    <t>e_w324064297*</t>
-  </si>
-  <si>
-    <t>p_w485873934</t>
-  </si>
-  <si>
-    <t>e_w485873934*</t>
-  </si>
-  <si>
-    <t>p_w485873968</t>
-  </si>
-  <si>
-    <t>e_w485873968*</t>
-  </si>
-  <si>
-    <t>p_w526897229</t>
-  </si>
-  <si>
-    <t>e_w526897229*</t>
-  </si>
-  <si>
-    <t>p_w577176545</t>
-  </si>
-  <si>
-    <t>e_w577176545*</t>
-  </si>
-  <si>
-    <t>p_w923418232</t>
-  </si>
-  <si>
-    <t>e_w923418232*</t>
-  </si>
-  <si>
-    <t>p_w1012817818</t>
-  </si>
-  <si>
-    <t>e_w1012817818*</t>
-  </si>
-  <si>
-    <t>p_w1015325412</t>
-  </si>
-  <si>
-    <t>e_w1015325412*</t>
-  </si>
-  <si>
-    <t>p_w1044735753</t>
-  </si>
-  <si>
-    <t>e_w1044735753*</t>
-  </si>
-  <si>
-    <t>p_w1238123371</t>
-  </si>
-  <si>
-    <t>e_w1238123371*</t>
-  </si>
-  <si>
-    <t>p_w1341647644</t>
-  </si>
-  <si>
-    <t>e_w1341647644*</t>
-  </si>
-  <si>
-    <t>p_IN290</t>
-  </si>
-  <si>
-    <t>e_IN290*</t>
-  </si>
-  <si>
-    <t>p_IN287</t>
-  </si>
-  <si>
-    <t>e_IN287*</t>
-  </si>
-  <si>
-    <t>p_IN286</t>
-  </si>
-  <si>
-    <t>e_IN286*</t>
-  </si>
-  <si>
-    <t>p_IN363</t>
-  </si>
-  <si>
-    <t>e_IN363*</t>
-  </si>
-  <si>
-    <t>p_IN285</t>
-  </si>
-  <si>
-    <t>e_IN285*</t>
-  </si>
-  <si>
-    <t>p_IN353</t>
-  </si>
-  <si>
-    <t>e_IN353*</t>
-  </si>
-  <si>
-    <t>p_IN317</t>
-  </si>
-  <si>
-    <t>e_IN317*</t>
-  </si>
-  <si>
-    <t>p_IN259</t>
-  </si>
-  <si>
-    <t>e_IN259*</t>
-  </si>
-  <si>
-    <t>p_IN325</t>
-  </si>
-  <si>
-    <t>e_IN325*</t>
-  </si>
-  <si>
-    <t>p_IN341</t>
-  </si>
-  <si>
-    <t>e_IN341*</t>
-  </si>
-  <si>
-    <t>p_IN315</t>
-  </si>
-  <si>
-    <t>e_IN315*</t>
-  </si>
-  <si>
-    <t>p_IN155</t>
-  </si>
-  <si>
-    <t>e_IN155*</t>
-  </si>
-  <si>
-    <t>p_IN263</t>
-  </si>
-  <si>
-    <t>e_IN263*</t>
-  </si>
-  <si>
-    <t>p_IN336</t>
-  </si>
-  <si>
-    <t>e_IN336*</t>
-  </si>
-  <si>
-    <t>p_IN320</t>
-  </si>
-  <si>
-    <t>e_IN320*</t>
-  </si>
-  <si>
-    <t>p_IN339</t>
-  </si>
-  <si>
-    <t>e_IN339*</t>
-  </si>
-  <si>
-    <t>p_IN179</t>
-  </si>
-  <si>
-    <t>e_IN179*</t>
-  </si>
-  <si>
-    <t>p_IN181</t>
-  </si>
-  <si>
-    <t>e_IN181*</t>
-  </si>
-  <si>
-    <t>p_IN262</t>
-  </si>
-  <si>
-    <t>e_IN262*</t>
-  </si>
-  <si>
-    <t>rez_spv_001</t>
-  </si>
-  <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>rez_spv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>rez_spv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>rez_spv_004</t>
-  </si>
-  <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>rez_spv_005</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>rez_spv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>rez_spv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>rez_spv_008</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>rez_spv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>rez_spv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>rez_spv_011</t>
-  </si>
-  <si>
-    <t>elc_spv_011</t>
-  </si>
-  <si>
-    <t>rez_spv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>rez_spv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
-    <t>rez_spv_014</t>
-  </si>
-  <si>
-    <t>elc_spv_014</t>
-  </si>
-  <si>
-    <t>rez_spv_015</t>
-  </si>
-  <si>
-    <t>elc_spv_015</t>
-  </si>
-  <si>
-    <t>rez_spv_016</t>
-  </si>
-  <si>
-    <t>elc_spv_016</t>
-  </si>
-  <si>
-    <t>rez_spv_017</t>
-  </si>
-  <si>
-    <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>rez_spv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
-  </si>
-  <si>
-    <t>rez_spv_019</t>
-  </si>
-  <si>
-    <t>elc_spv_019</t>
-  </si>
-  <si>
-    <t>rez_spv_020</t>
-  </si>
-  <si>
-    <t>elc_spv_020</t>
-  </si>
-  <si>
-    <t>rez_spv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
-    <t>rez_spv_022</t>
-  </si>
-  <si>
-    <t>elc_spv_022</t>
-  </si>
-  <si>
-    <t>rez_spv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>rez_spv_024</t>
-  </si>
-  <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
-    <t>rez_spv_025</t>
-  </si>
-  <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>rez_spv_026</t>
-  </si>
-  <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
-    <t>rez_spv_027</t>
-  </si>
-  <si>
-    <t>elc_spv_027</t>
-  </si>
-  <si>
-    <t>rez_spv_028</t>
-  </si>
-  <si>
-    <t>elc_spv_028</t>
-  </si>
-  <si>
-    <t>rez_spv_029</t>
-  </si>
-  <si>
-    <t>elc_spv_029</t>
-  </si>
-  <si>
-    <t>rez_spv_030</t>
-  </si>
-  <si>
-    <t>elc_spv_030</t>
-  </si>
-  <si>
-    <t>rez_spv_031</t>
-  </si>
-  <si>
-    <t>elc_spv_031</t>
-  </si>
-  <si>
-    <t>rez_spv_032</t>
-  </si>
-  <si>
-    <t>elc_spv_032</t>
-  </si>
-  <si>
-    <t>rez_spv_033</t>
-  </si>
-  <si>
-    <t>elc_spv_033</t>
-  </si>
-  <si>
-    <t>rez_spv_034</t>
-  </si>
-  <si>
-    <t>elc_spv_034</t>
-  </si>
-  <si>
-    <t>rez_spv_035</t>
-  </si>
-  <si>
-    <t>elc_spv_035</t>
-  </si>
-  <si>
-    <t>rez_spv_036</t>
-  </si>
-  <si>
-    <t>elc_spv_036</t>
-  </si>
-  <si>
-    <t>rez_spv_037</t>
-  </si>
-  <si>
-    <t>elc_spv_037</t>
-  </si>
-  <si>
-    <t>rez_spv_038</t>
-  </si>
-  <si>
-    <t>elc_spv_038</t>
-  </si>
-  <si>
-    <t>rez_spv_039</t>
-  </si>
-  <si>
-    <t>elc_spv_039</t>
-  </si>
-  <si>
-    <t>rez_spv_040</t>
-  </si>
-  <si>
-    <t>elc_spv_040</t>
-  </si>
-  <si>
-    <t>rez_spv_041</t>
-  </si>
-  <si>
-    <t>elc_spv_041</t>
-  </si>
-  <si>
-    <t>rez_spv_042</t>
-  </si>
-  <si>
-    <t>elc_spv_042</t>
-  </si>
-  <si>
-    <t>rez_spv_043</t>
-  </si>
-  <si>
-    <t>elc_spv_043</t>
-  </si>
-  <si>
-    <t>rez_spv_044</t>
-  </si>
-  <si>
-    <t>elc_spv_044</t>
-  </si>
-  <si>
-    <t>rez_spv_045</t>
-  </si>
-  <si>
-    <t>elc_spv_045</t>
-  </si>
-  <si>
-    <t>rez_spv_046</t>
-  </si>
-  <si>
-    <t>elc_spv_046</t>
-  </si>
-  <si>
-    <t>rez_spv_047</t>
-  </si>
-  <si>
-    <t>elc_spv_047</t>
-  </si>
-  <si>
-    <t>rez_spv_048</t>
-  </si>
-  <si>
-    <t>elc_spv_048</t>
-  </si>
-  <si>
-    <t>rez_spv_049</t>
-  </si>
-  <si>
-    <t>elc_spv_049</t>
-  </si>
-  <si>
-    <t>rez_spv_050</t>
-  </si>
-  <si>
-    <t>elc_spv_050</t>
-  </si>
-  <si>
-    <t>rez_spv_051</t>
-  </si>
-  <si>
-    <t>elc_spv_051</t>
-  </si>
-  <si>
-    <t>rez_spv_052</t>
-  </si>
-  <si>
-    <t>elc_spv_052</t>
-  </si>
-  <si>
-    <t>rez_spv_053</t>
-  </si>
-  <si>
-    <t>elc_spv_053</t>
-  </si>
-  <si>
-    <t>rez_spv_054</t>
-  </si>
-  <si>
-    <t>elc_spv_054</t>
-  </si>
-  <si>
-    <t>rez_spv_055</t>
-  </si>
-  <si>
-    <t>elc_spv_055</t>
-  </si>
-  <si>
-    <t>rez_spv_056</t>
-  </si>
-  <si>
-    <t>elc_spv_056</t>
-  </si>
-  <si>
-    <t>rez_spv_057</t>
-  </si>
-  <si>
-    <t>elc_spv_057</t>
-  </si>
-  <si>
-    <t>rez_spv_058</t>
-  </si>
-  <si>
-    <t>elc_spv_058</t>
-  </si>
-  <si>
-    <t>rez_spv_059</t>
-  </si>
-  <si>
-    <t>elc_spv_059</t>
-  </si>
-  <si>
-    <t>rez_spv_060</t>
-  </si>
-  <si>
-    <t>elc_spv_060</t>
-  </si>
-  <si>
-    <t>rez_spv_061</t>
-  </si>
-  <si>
-    <t>elc_spv_061</t>
-  </si>
-  <si>
-    <t>rez_spv_062</t>
-  </si>
-  <si>
-    <t>elc_spv_062</t>
-  </si>
-  <si>
-    <t>rez_spv_063</t>
-  </si>
-  <si>
-    <t>elc_spv_063</t>
-  </si>
-  <si>
-    <t>rez_spv_064</t>
-  </si>
-  <si>
-    <t>elc_spv_064</t>
-  </si>
-  <si>
-    <t>rez_spv_065</t>
-  </si>
-  <si>
-    <t>elc_spv_065</t>
-  </si>
-  <si>
-    <t>rez_spv_066</t>
-  </si>
-  <si>
-    <t>elc_spv_066</t>
-  </si>
-  <si>
-    <t>rez_spv_067</t>
-  </si>
-  <si>
-    <t>elc_spv_067</t>
-  </si>
-  <si>
-    <t>rez_spv_068</t>
-  </si>
-  <si>
-    <t>elc_spv_068</t>
-  </si>
-  <si>
-    <t>rez_spv_069</t>
-  </si>
-  <si>
-    <t>elc_spv_069</t>
-  </si>
-  <si>
-    <t>rez_spv_070</t>
-  </si>
-  <si>
-    <t>elc_spv_070</t>
-  </si>
-  <si>
-    <t>rez_spv_071</t>
-  </si>
-  <si>
-    <t>elc_spv_071</t>
-  </si>
-  <si>
-    <t>rez_spv_072</t>
-  </si>
-  <si>
-    <t>elc_spv_072</t>
-  </si>
-  <si>
-    <t>rez_spv_073</t>
-  </si>
-  <si>
-    <t>elc_spv_073</t>
-  </si>
-  <si>
-    <t>rez_spv_074</t>
-  </si>
-  <si>
-    <t>elc_spv_074</t>
-  </si>
-  <si>
-    <t>rez_spv_075</t>
-  </si>
-  <si>
-    <t>elc_spv_075</t>
-  </si>
-  <si>
-    <t>rez_spv_076</t>
-  </si>
-  <si>
-    <t>elc_spv_076</t>
-  </si>
-  <si>
-    <t>rez_spv_077</t>
-  </si>
-  <si>
-    <t>elc_spv_077</t>
-  </si>
-  <si>
-    <t>rez_spv_078</t>
-  </si>
-  <si>
-    <t>elc_spv_078</t>
-  </si>
-  <si>
-    <t>rez_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>rez_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>rez_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>rez_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>rez_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>rez_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>rez_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>rez_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>rez_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>rez_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>rez_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>rez_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>rez_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>rez_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>rez_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>rez_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>rez_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>rez_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>rez_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>rez_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>rez_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>rez_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>rez_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>rez_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>rez_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>rez_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>rez_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>rez_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>rez_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>rez_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>rez_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>rez_won_032</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>rez_won_033</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>rez_won_034</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>rez_won_035</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>rez_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>rez_won_037</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>rez_won_038</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>rez_won_039</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>rez_won_040</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>rez_won_041</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>rez_won_042</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>rez_won_043</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>rez_won_044</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>rez_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>rez_won_046</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>rez_won_047</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>rez_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>rez_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>rez_won_050</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>rez_won_051</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>rez_won_052</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>rez_won_053</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>rez_won_054</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>rez_won_055</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>rez_won_056</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>rez_won_057</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>rez_won_058</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>rez_won_059</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>rez_won_060</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>rez_won_061</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>rez_won_062</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>rez_won_063</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>rez_won_064</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>rez_won_065</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>rez_won_066</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>rez_won_067</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>rez_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>rez_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>rez_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>rez_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>rez_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>rez_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>rez_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>rez_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>rez_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>rez_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>rez_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>rez_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>rez_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>rez_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>rez_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>rez_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>rez_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>rez_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>rez_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>rez_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>rez_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>rez_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>rez_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>rez_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
+    <t>p_w97392607-765_IND</t>
+  </si>
+  <si>
+    <t>e_w97392607-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w100470285-765_IND</t>
+  </si>
+  <si>
+    <t>e_w100470285-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w105373531-765_IND</t>
+  </si>
+  <si>
+    <t>e_w105373531-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w131484738-765_IND</t>
+  </si>
+  <si>
+    <t>e_w131484738-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w192782338-765_IND</t>
+  </si>
+  <si>
+    <t>e_w192782338-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w193216698-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w195459361-765_IND</t>
+  </si>
+  <si>
+    <t>e_w195459361-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196933682-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w201845280-765_IND</t>
+  </si>
+  <si>
+    <t>e_w201845280-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w202980838-765_IND</t>
+  </si>
+  <si>
+    <t>e_w202980838-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w209806624-765_IND</t>
+  </si>
+  <si>
+    <t>e_w209806624-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w209826798-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>e_w245128370-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w247861059-765_IND</t>
+  </si>
+  <si>
+    <t>e_w247861059-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>e_w248385304-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>e_w274106872-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>e_w293597835-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311103617-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w311118424-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311118424-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311176519-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311571096-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w311933111-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311933111-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311954703-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1246177377-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1246177377-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315477169-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315823978-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w315824842-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>e_w316463122-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>e_w318050929-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w318090288-765_IND</t>
+  </si>
+  <si>
+    <t>e_w318090288-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>e_w319423421-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w328548895-765_IND</t>
+  </si>
+  <si>
+    <t>e_w328548895-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>e_w331275940-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>e_w352619220-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w353914761-765_IND</t>
+  </si>
+  <si>
+    <t>e_w353914761-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w353914865-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>e_w354062412-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w357515226-765_IND</t>
+  </si>
+  <si>
+    <t>e_w357515226-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>e_w360424761-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>e_w386018740-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w408924420-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w408924427-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924427-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w409798382-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409798382-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>e_w417569420-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w420797421-765_IND</t>
+  </si>
+  <si>
+    <t>e_w420797421-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w422204218-765_IND</t>
+  </si>
+  <si>
+    <t>e_w422204218-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w423166766-765_IND</t>
+  </si>
+  <si>
+    <t>e_w423166766-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w423702239-765_IND</t>
+  </si>
+  <si>
+    <t>e_w423702239-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w425101516-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425101516-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w453513742-765_IND</t>
+  </si>
+  <si>
+    <t>e_w453513742-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w466424134-765_IND</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w801704865-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w477691456-765_IND</t>
+  </si>
+  <si>
+    <t>e_w477691456-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w514344408-765_IND</t>
+  </si>
+  <si>
+    <t>e_w514344408-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w521570801-765_IND</t>
+  </si>
+  <si>
+    <t>e_w521570801-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w551402699-765_IND</t>
+  </si>
+  <si>
+    <t>e_w551402699-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w607439318-765_IND</t>
+  </si>
+  <si>
+    <t>e_w607439318-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w608461884-765_IND</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>e_w631917408-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w654736039-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w655683221-765_IND</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w686891085-765_IND</t>
+  </si>
+  <si>
+    <t>e_w686891085-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>e_w688672711-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w751947947-765_IND</t>
+  </si>
+  <si>
+    <t>e_w751947947-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w781425567-765_IND</t>
+  </si>
+  <si>
+    <t>e_w781425567-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w793144832-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_w840600239-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>e_w910151268-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>e_w923365745-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1001700959-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1074489047-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1077819664-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1077819664-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1127651311-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1143180503-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1206014676-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1329624553-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1329624553-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1336628403-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1336628403-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1341291951-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w1415199647-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1415199647-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN532-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN532-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN10-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN10-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN372-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN372-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN328-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN328-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN373-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN373-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN367-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN367-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN289-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN289-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN323-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN323-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN365-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN346-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN346-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN350-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN350-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN370-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN370-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN380-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN380-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN388-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN388-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN343-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN343-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN136-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN136-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN473-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN473-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN244-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN244-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN489-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN489-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN321-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN321-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN276-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN276-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN327-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN327-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN288-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN288-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN329-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN329-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN270-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN264-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN264-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN272-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN278-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN278-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN612-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN612-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN394-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN394-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN387-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN387-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN382-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN382-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN399-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN399-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN403-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN403-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN405-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN405-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN393-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN393-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN392-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN392-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN390-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN390-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN384-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN384-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN381-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN381-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN395-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN395-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN376-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN376-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN402-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN402-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN397-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN397-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN404-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN404-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN412-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN412-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN247-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN247-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN250-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN250-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN249-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN249-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN246-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN246-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN490-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN490-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN488-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN488-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN583-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN583-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN586-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN586-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN555-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN555-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN293-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN293-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN230-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN230-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN233-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN233-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN400-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN400-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN396-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN396-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN391-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN391-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN205-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN205-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN206-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN206-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN202-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN202-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN101-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN101-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN105-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN105-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN100-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN100-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN85-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN85-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN225-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN225-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN196-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN196-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN229-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN229-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN609-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN609-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN610-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN610-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN607-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN607-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN617-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN617-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN306-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN306-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN300-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN300-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN142-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN142-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN200-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN200-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN171-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN171-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN541-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN541-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN642-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN642-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN284-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN284-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN239-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN282-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN282-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN292-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN292-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN295-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN295-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN529-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN529-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN457-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN457-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN540-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN540-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN240-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN240-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN280-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN280-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN279-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN279-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN539-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN539-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN537-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN537-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN476-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN476-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN439-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN439-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN548-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN548-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN416-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN416-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN413-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN413-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN742-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN742-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN749-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN749-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN684-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN135-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN135-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN685-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN685-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN159-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN159-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN161-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN161-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN164-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN164-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN163-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN187-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN187-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN197-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN197-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN807-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN807-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN801-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN801-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN803-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN803-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN798-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN137-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN137-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN139-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN139-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN148-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN148-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN191-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN191-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN73-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN73-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN42-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN42-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN108-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN108-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w492377703-765_IND</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN375-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN375-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN107-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN107-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN307-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN307-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN298-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN298-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN275-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN275-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN268-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN268-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN253-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN253-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN255-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN255-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN222-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN222-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN201-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN201-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN190-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN190-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN178-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN178-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN254-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN254-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN116-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN116-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN126-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN126-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN123-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN123-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN120-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN120-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN351-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN351-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN243-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN243-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN277-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN277-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN401-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN401-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN535-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN535-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN578-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN578-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN283-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN283-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN599-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN203-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN203-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN180-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN180-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN104-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN104-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN659-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN160-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN160-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN174-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN174-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN312-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN312-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN167-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN167-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w196563905-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196563905-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN748-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN748-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN267-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN267-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN215-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN215-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN199-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN199-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN194-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN194-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN809-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN809-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN808-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN808-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN806-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN806-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN146-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN146-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN138-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN138-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN140-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN140-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN94-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN94-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN302-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN302-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN269-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN269-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN258-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN258-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN232-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN232-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN257-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN257-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN217-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN217-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN198-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN198-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN183-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN183-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN175-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN175-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN128-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN128-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN125-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN125-765_IND*</t>
+  </si>
+  <si>
+    <t>p_IN121-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN121-765_IND*</t>
+  </si>
+  <si>
+    <t>p_w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>e_w116541259-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w203673991-400_IND</t>
+  </si>
+  <si>
+    <t>e_w203673991-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w239498664-400_IND</t>
+  </si>
+  <si>
+    <t>e_w239498664-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w374367235-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w375084335-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375084335-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375941438-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w439006823-400_IND</t>
+  </si>
+  <si>
+    <t>e_w439006823-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w465787206-400_IND</t>
+  </si>
+  <si>
+    <t>e_w465787206-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>e_w610646823-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1099365556-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365556-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365579-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1265489491-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1265489491-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1265496720-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1265496720-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN177-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN177-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN440-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN265-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN265-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN145-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN176-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN176-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN260-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN260-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN386-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN386-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w50885643-400_IND</t>
+  </si>
+  <si>
+    <t>e_w50885643-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w92360278-400_IND</t>
+  </si>
+  <si>
+    <t>e_w92360278-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w92994753-400_IND</t>
+  </si>
+  <si>
+    <t>e_w92994753-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w93160503-400_IND</t>
+  </si>
+  <si>
+    <t>e_w93160503-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w94199110-400_IND</t>
+  </si>
+  <si>
+    <t>e_w94199110-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w96821783-400_IND</t>
+  </si>
+  <si>
+    <t>e_w96821783-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>e_w97392607-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w118228036-400_IND</t>
+  </si>
+  <si>
+    <t>e_w118228036-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w149822703-400_IND</t>
+  </si>
+  <si>
+    <t>e_w149822703-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>e_w205942950-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w209806624-400_IND</t>
+  </si>
+  <si>
+    <t>e_w209806624-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w209806650-400_IND</t>
+  </si>
+  <si>
+    <t>e_w209806650-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w324059200-400_IND</t>
+  </si>
+  <si>
+    <t>e_w324059200-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w324064297-400_IND</t>
+  </si>
+  <si>
+    <t>e_w324064297-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w409798382-400_IND</t>
+  </si>
+  <si>
+    <t>e_w409798382-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>e_w485873934-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>e_w485873968-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>e_w526897229-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w577176545-400_IND</t>
+  </si>
+  <si>
+    <t>e_w577176545-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w923418232-400_IND</t>
+  </si>
+  <si>
+    <t>e_w923418232-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1012817818-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1012817818-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1015325412-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1015325412-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1044735753-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1238123371-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1238123371-400_IND*</t>
+  </si>
+  <si>
+    <t>p_w1341647644-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1341647644-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN290-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN287-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN287-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN286-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN286-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN363-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN363-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN285-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN285-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN353-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN353-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN317-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN317-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN259-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN259-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN325-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN325-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN341-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN341-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN315-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN315-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN155-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN155-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN263-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN263-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN336-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN336-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN320-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN320-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN339-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN339-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN179-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN179-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN181-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN181-400_IND*</t>
+  </si>
+  <si>
+    <t>p_IN262-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN262-400_IND*</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_001</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_002</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_003</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_004</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_005</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_006</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_007</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_008</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_009</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_010</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_011</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_012</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_013</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_014</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_015</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_016</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_017</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_018</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_019</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_020</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_021</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_022</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_023</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_024</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_025</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_026</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_027</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_028</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_029</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_030</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_031</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_032</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_033</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_034</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_035</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_036</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_037</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_038</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_039</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_040</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_041</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_042</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_043</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_044</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_045</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_046</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_047</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_048</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_049</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_050</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_051</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_052</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_053</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_054</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_055</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_056</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_057</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_058</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_059</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_060</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_061</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_062</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_063</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_064</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_065</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_066</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_067</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_068</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_069</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_070</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_071</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_072</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_073</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_074</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_075</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_076</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_077</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>rez_spv_IND_078</t>
+  </si>
+  <si>
+    <t>elc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>rez_won_IND_001</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>rez_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>rez_won_IND_003</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>rez_won_IND_004</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>rez_won_IND_005</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>rez_won_IND_006</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>rez_won_IND_007</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>rez_won_IND_008</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>rez_won_IND_009</t>
+  </si>
+  <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>rez_won_IND_010</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>rez_won_IND_011</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>rez_won_IND_012</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>rez_won_IND_013</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>rez_won_IND_014</t>
+  </si>
+  <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>rez_won_IND_015</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>rez_won_IND_016</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>rez_won_IND_017</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>rez_won_IND_018</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>rez_won_IND_019</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>rez_won_IND_020</t>
+  </si>
+  <si>
+    <t>elc_won_IND_020</t>
+  </si>
+  <si>
+    <t>rez_won_IND_021</t>
+  </si>
+  <si>
+    <t>elc_won_IND_021</t>
+  </si>
+  <si>
+    <t>rez_won_IND_022</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>rez_won_IND_023</t>
+  </si>
+  <si>
+    <t>elc_won_IND_023</t>
+  </si>
+  <si>
+    <t>rez_won_IND_024</t>
+  </si>
+  <si>
+    <t>elc_won_IND_024</t>
+  </si>
+  <si>
+    <t>rez_won_IND_025</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>rez_won_IND_026</t>
+  </si>
+  <si>
+    <t>elc_won_IND_026</t>
+  </si>
+  <si>
+    <t>rez_won_IND_027</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>rez_won_IND_028</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>rez_won_IND_029</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>rez_won_IND_030</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>rez_won_IND_031</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>rez_won_IND_032</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>rez_won_IND_033</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>rez_won_IND_034</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>rez_won_IND_035</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>rez_won_IND_036</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>rez_won_IND_037</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>rez_won_IND_038</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>rez_won_IND_039</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>rez_won_IND_040</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>rez_won_IND_041</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>rez_won_IND_042</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>rez_won_IND_043</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>rez_won_IND_044</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>rez_won_IND_045</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>rez_won_IND_046</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>rez_won_IND_047</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>rez_won_IND_048</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>rez_won_IND_049</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>rez_won_IND_050</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>rez_won_IND_051</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>rez_won_IND_052</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>rez_won_IND_053</t>
+  </si>
+  <si>
+    <t>elc_won_IND_053</t>
+  </si>
+  <si>
+    <t>rez_won_IND_054</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>rez_won_IND_055</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>rez_won_IND_056</t>
+  </si>
+  <si>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>rez_won_IND_057</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>rez_won_IND_058</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>rez_won_IND_059</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>rez_won_IND_060</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>rez_won_IND_061</t>
+  </si>
+  <si>
+    <t>elc_won_IND_061</t>
+  </si>
+  <si>
+    <t>rez_won_IND_062</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>rez_won_IND_063</t>
+  </si>
+  <si>
+    <t>elc_won_IND_063</t>
+  </si>
+  <si>
+    <t>rez_won_IND_064</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>rez_won_IND_065</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>rez_won_IND_066</t>
+  </si>
+  <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>rez_won_IND_067</t>
+  </si>
+  <si>
+    <t>elc_won_IND_067</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_004</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_006</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_007</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_009</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_011</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_013</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_016</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_018</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_021</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_023</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>rez_wof_IND_024</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
   </si>
 </sst>
 </file>
@@ -3524,9 +3548,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3564,7 +3588,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3670,7 +3694,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3812,7 +3836,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4140,39 +4164,39 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D28" t="str">
         <f>B28</f>
@@ -4181,7 +4205,7 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D29" t="str">
         <f>B29</f>
@@ -4190,7 +4214,7 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D30" t="str">
         <f>B30</f>
@@ -4199,7 +4223,7 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D31" t="str">
         <f>B31</f>
@@ -4208,39 +4232,39 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D36" t="str">
         <f>B36</f>
@@ -4249,7 +4273,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D37" t="str">
         <f>B37</f>
@@ -4265,8 +4289,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9693C71A-E66B-4680-8C0A-0A5A6E3B7B50}">
-  <dimension ref="B9:E523"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCAE60E3-87AA-48DB-9596-99D870E1D763}">
+  <dimension ref="B9:E527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -11467,6 +11491,62 @@
         <v>1129</v>
       </c>
       <c r="E523" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="524" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B524" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E524" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="525" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B525" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E525" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="526" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B526" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E526" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="527" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B527" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E527" t="s">
         <v>105</v>
       </c>
     </row>
@@ -11526,7 +11606,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -11535,45 +11615,45 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -11581,7 +11661,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -11589,57 +11669,57 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B12" s="3"/>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D14" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
@@ -11647,13 +11727,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
@@ -11661,121 +11741,121 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
         <v>24</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" t="s">
         <v>37</v>
       </c>
-      <c r="H20" t="s">
-        <v>44</v>
-      </c>
       <c r="I20" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
@@ -12053,18 +12133,18 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92A78C63-B196-40CF-A755-100788F9F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{057152C6-B1BD-49E3-93F8-CC987E77E18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4289,7 +4289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCAE60E3-87AA-48DB-9596-99D870E1D763}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D94B7C-6D86-4BE1-BCC9-69CCFAA54351}">
   <dimension ref="B9:E527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{057152C6-B1BD-49E3-93F8-CC987E77E18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5198CB9F-72B1-4AFF-9C82-CD93B879CB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4289,7 +4289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D94B7C-6D86-4BE1-BCC9-69CCFAA54351}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052A67DB-5B36-46AE-B6B7-3F3113D4A428}">
   <dimension ref="B9:E527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5198CB9F-72B1-4AFF-9C82-CD93B879CB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA6EE9F6-AFBB-4622-BBA3-8764C0F37168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3548,9 +3548,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3588,7 +3588,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3694,7 +3694,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3836,7 +3836,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4289,7 +4289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052A67DB-5B36-46AE-B6B7-3F3113D4A428}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0263C5B-7767-441F-9654-2D9D165A9B9C}">
   <dimension ref="B9:E527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/Sets-vervestacks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA6EE9F6-AFBB-4622-BBA3-8764C0F37168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD745346-BB89-4491-AE10-29FF4B5991BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4289,7 +4289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0263C5B-7767-441F-9654-2D9D165A9B9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33AA37E-60E2-49C1-B288-ECACA0AF22E3}">
   <dimension ref="B9:E527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
